--- a/fppos/products/product.xlsx
+++ b/fppos/products/product.xlsx
@@ -3,22 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B892A5-1EE9-4655-92FD-7EDBE021ED77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D5B9CB-FDBA-4674-8BDA-7963606CF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachSanPham_KV07012026-1608" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="450">
-  <si>
-    <t>Khác</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="434">
   <si>
     <t>WebsiteFPGV0002</t>
   </si>
@@ -35,9 +45,6 @@
     <t>COMBO Ức gà viên 200gr - Website</t>
   </si>
   <si>
-    <t>BURGER</t>
-  </si>
-  <si>
     <t>PGBG07</t>
   </si>
   <si>
@@ -74,9 +81,6 @@
     <t>FP0021:1|FP0024:1|FP0022:1|FF0026:1|FP0027:1</t>
   </si>
   <si>
-    <t>Cơm hộp</t>
-  </si>
-  <si>
     <t>GLAN07</t>
   </si>
   <si>
@@ -92,18 +96,12 @@
     <t>WebsiteFPGV0009</t>
   </si>
   <si>
-    <t>Ức gà 100g</t>
-  </si>
-  <si>
     <t>FP0001</t>
   </si>
   <si>
     <t>Ức gà sinh tố 100gr</t>
   </si>
   <si>
-    <t>Sốt</t>
-  </si>
-  <si>
     <t>WebsiteSS0009</t>
   </si>
   <si>
@@ -116,9 +114,6 @@
     <t>Hủ sốt Tiêu Đen 250ml - Website</t>
   </si>
   <si>
-    <t>FP GO</t>
-  </si>
-  <si>
     <t>FPG026</t>
   </si>
   <si>
@@ -173,9 +168,6 @@
     <t>CƠM GÀ HẢI NAM</t>
   </si>
   <si>
-    <t>Cơm cafe</t>
-  </si>
-  <si>
     <t>FPCF0016</t>
   </si>
   <si>
@@ -188,9 +180,6 @@
     <t>CD - CƠM GÀ HẢI NAM</t>
   </si>
   <si>
-    <t>Farmers</t>
-  </si>
-  <si>
     <t>I0018593</t>
   </si>
   <si>
@@ -362,9 +351,6 @@
     <t>CD - MỲ Ý BÒ BẲM</t>
   </si>
   <si>
-    <t>Ức gà viên</t>
-  </si>
-  <si>
     <t>FPGV0011</t>
   </si>
   <si>
@@ -470,18 +456,12 @@
     <t>CF-CÀ RI BÒ KHOAI NƯỚNG</t>
   </si>
   <si>
-    <t>BISCOTTI</t>
-  </si>
-  <si>
     <t>BCT10</t>
   </si>
   <si>
     <t>GRANOLA 200gr</t>
   </si>
   <si>
-    <t>STEAK</t>
-  </si>
-  <si>
     <t>FPSTEAK7</t>
   </si>
   <si>
@@ -554,9 +534,6 @@
     <t>GLAN01:1|GLAN02:2|GLAN03:2</t>
   </si>
   <si>
-    <t>Ức gà 150g</t>
-  </si>
-  <si>
     <t>FP0061503</t>
   </si>
   <si>
@@ -869,9 +846,6 @@
     <t>150g Gà Tiềm</t>
   </si>
   <si>
-    <t>COMBO THÙNG</t>
-  </si>
-  <si>
     <t>BOX01</t>
   </si>
   <si>
@@ -962,9 +936,6 @@
     <t>Steak Bò Mỹ Fitpack - Không sốt</t>
   </si>
   <si>
-    <t>Rau củ ăn liền</t>
-  </si>
-  <si>
     <t>FPRC01</t>
   </si>
   <si>
@@ -980,9 +951,6 @@
     <t>SP000002:1|SP000004:1|SP000006:1</t>
   </si>
   <si>
-    <t>Bình Nước</t>
-  </si>
-  <si>
     <t>FPBNTIM</t>
   </si>
   <si>
@@ -1101,9 +1069,6 @@
   </si>
   <si>
     <t>BÚN XÀO SINGAPORE</t>
-  </si>
-  <si>
-    <t>DIMSUM</t>
   </si>
   <si>
     <t>DS0005</t>
@@ -1750,36 +1715,36 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>442</v>
-      </c>
-      <c r="B2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
       </c>
       <c r="E2" s="1">
         <v>49000</v>
@@ -1787,16 +1752,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
         <v>49000</v>
@@ -1804,16 +1769,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>442</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
       </c>
       <c r="E4" s="1">
         <v>392000</v>
@@ -1821,36 +1786,36 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>443</v>
-      </c>
-      <c r="B5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
       </c>
       <c r="E5" s="1">
         <v>120000</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>442</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
         <v>40000</v>
@@ -1858,16 +1823,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>442</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
         <v>40000</v>
@@ -1875,76 +1840,76 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>442</v>
-      </c>
-      <c r="B8" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1">
         <v>300000</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>442</v>
-      </c>
-      <c r="B9" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1">
         <v>165000</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>443</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>85000</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>442</v>
-      </c>
-      <c r="B11" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
         <v>49000</v>
@@ -1952,16 +1917,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B12" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1">
         <v>196000</v>
@@ -1969,16 +1934,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>442</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1">
         <v>18000</v>
@@ -1986,16 +1951,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>442</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1">
         <v>50000</v>
@@ -2003,16 +1968,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>442</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1">
         <v>50000</v>
@@ -2020,16 +1985,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>442</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1">
         <v>44000</v>
@@ -2037,16 +2002,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>442</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1">
         <v>40000</v>
@@ -2054,16 +2019,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>442</v>
-      </c>
-      <c r="B18" t="s">
+        <v>426</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
       </c>
       <c r="E18" s="1">
         <v>44000</v>
@@ -2071,16 +2036,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>442</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1">
         <v>59000</v>
@@ -2088,16 +2053,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>442</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1">
         <v>59000</v>
@@ -2105,16 +2070,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1">
         <v>59000</v>
@@ -2122,16 +2087,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>442</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1">
         <v>59000</v>
@@ -2139,16 +2104,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>442</v>
-      </c>
-      <c r="B23" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E23" s="1">
         <v>59000</v>
@@ -2156,16 +2121,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>442</v>
-      </c>
-      <c r="B24" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1">
         <v>59000</v>
@@ -2173,16 +2138,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>442</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E25" s="1">
         <v>59000</v>
@@ -2190,16 +2155,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>442</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B26">
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E26" s="1">
         <v>59000</v>
@@ -2207,16 +2172,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>442</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E27" s="1">
         <v>36750</v>
@@ -2224,16 +2189,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>442</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E28" s="1">
         <v>36750</v>
@@ -2241,16 +2206,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E29" s="1">
         <v>36750</v>
@@ -2258,16 +2223,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>442</v>
-      </c>
-      <c r="B30" t="s">
+        <v>426</v>
+      </c>
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
         <v>57</v>
-      </c>
-      <c r="C30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>65</v>
       </c>
       <c r="E30" s="1">
         <v>36750</v>
@@ -2275,16 +2240,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B31" t="s">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>49000</v>
@@ -2292,16 +2257,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>442</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1">
         <v>36750</v>
@@ -2309,16 +2274,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>442</v>
-      </c>
-      <c r="B33" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E33" s="1">
         <v>36750</v>
@@ -2326,16 +2291,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>442</v>
-      </c>
-      <c r="B34" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E34" s="1">
         <v>36750</v>
@@ -2343,16 +2308,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>442</v>
-      </c>
-      <c r="B35" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E35" s="1">
         <v>36750</v>
@@ -2360,16 +2325,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>442</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E36" s="1">
         <v>36750</v>
@@ -2377,16 +2342,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>442</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E37" s="1">
         <v>37500</v>
@@ -2394,16 +2359,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>442</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1">
         <v>36750</v>
@@ -2411,16 +2376,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>442</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E39" s="1">
         <v>36750</v>
@@ -2428,16 +2393,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>442</v>
-      </c>
-      <c r="B40" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E40" s="1">
         <v>36750</v>
@@ -2445,16 +2410,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>442</v>
-      </c>
-      <c r="B41" t="s">
-        <v>57</v>
+        <v>426</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E41" s="1">
         <v>36750</v>
@@ -2462,16 +2427,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>442</v>
-      </c>
-      <c r="B42" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E42" s="1">
         <v>58000</v>
@@ -2479,16 +2444,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>442</v>
-      </c>
-      <c r="B43" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1">
         <v>58000</v>
@@ -2496,16 +2461,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>442</v>
-      </c>
-      <c r="B44" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E44" s="1">
         <v>59000</v>
@@ -2513,16 +2478,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>442</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E45" s="1">
         <v>59000</v>
@@ -2530,16 +2495,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>442</v>
-      </c>
-      <c r="B46" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E46" s="1">
         <v>59000</v>
@@ -2547,16 +2512,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>442</v>
-      </c>
-      <c r="B47" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B47">
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E47" s="1">
         <v>59000</v>
@@ -2564,16 +2529,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>442</v>
-      </c>
-      <c r="B48" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B48">
+        <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E48" s="1">
         <v>69000</v>
@@ -2581,16 +2546,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>442</v>
-      </c>
-      <c r="B49" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E49" s="1">
         <v>59000</v>
@@ -2598,16 +2563,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>442</v>
-      </c>
-      <c r="B50" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B50">
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E50" s="1">
         <v>36000</v>
@@ -2615,16 +2580,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>442</v>
-      </c>
-      <c r="B51" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E51" s="1">
         <v>38000</v>
@@ -2632,16 +2597,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>442</v>
-      </c>
-      <c r="B52" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B52">
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E52" s="1">
         <v>36000</v>
@@ -2649,16 +2614,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>442</v>
-      </c>
-      <c r="B53" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E53" s="1">
         <v>38000</v>
@@ -2666,16 +2631,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>442</v>
-      </c>
-      <c r="B54" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E54" s="1">
         <v>37000</v>
@@ -2683,16 +2648,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>442</v>
-      </c>
-      <c r="B55" t="s">
-        <v>52</v>
+        <v>426</v>
+      </c>
+      <c r="B55">
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E55" s="1">
         <v>35000</v>
@@ -2700,76 +2665,76 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>443</v>
-      </c>
-      <c r="B56" t="s">
-        <v>115</v>
+        <v>427</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E56" s="1">
         <v>588000</v>
       </c>
       <c r="F56" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>443</v>
-      </c>
-      <c r="B57" t="s">
-        <v>115</v>
+        <v>427</v>
+      </c>
+      <c r="B57">
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E57" s="1">
         <v>392000</v>
       </c>
       <c r="F57" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>443</v>
-      </c>
-      <c r="B58" t="s">
-        <v>115</v>
+        <v>427</v>
+      </c>
+      <c r="B58">
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E58" s="1">
         <v>196000</v>
       </c>
       <c r="F58" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>442</v>
-      </c>
-      <c r="B59" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E59" s="1">
         <v>5000</v>
@@ -2777,16 +2742,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>442</v>
-      </c>
-      <c r="B60" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -2794,16 +2759,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>442</v>
-      </c>
-      <c r="B61" t="s">
-        <v>115</v>
+        <v>426</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E61" s="1">
         <v>49000</v>
@@ -2811,16 +2776,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>442</v>
-      </c>
-      <c r="B62" t="s">
-        <v>115</v>
+        <v>426</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E62" s="1">
         <v>49000</v>
@@ -2828,16 +2793,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>442</v>
-      </c>
-      <c r="B63" t="s">
-        <v>115</v>
+        <v>426</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E63" s="1">
         <v>49000</v>
@@ -2845,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>442</v>
-      </c>
-      <c r="B64" t="s">
-        <v>115</v>
+        <v>426</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E64" s="1">
         <v>49000</v>
@@ -2862,16 +2827,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>442</v>
-      </c>
-      <c r="B65" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E65" s="1">
         <v>50000</v>
@@ -2879,16 +2844,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>442</v>
-      </c>
-      <c r="B66" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E66" s="1">
         <v>50000</v>
@@ -2896,16 +2861,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>442</v>
-      </c>
-      <c r="B67" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E67" s="1">
         <v>40000</v>
@@ -2913,16 +2878,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>442</v>
-      </c>
-      <c r="B68" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B68">
+        <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E68" s="1">
         <v>40000</v>
@@ -2930,16 +2895,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>442</v>
-      </c>
-      <c r="B69" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E69" s="1">
         <v>44000</v>
@@ -2947,16 +2912,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>442</v>
-      </c>
-      <c r="B70" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B70">
+        <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E70" s="1">
         <v>40000</v>
@@ -2964,16 +2929,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>442</v>
-      </c>
-      <c r="B71" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B71">
+        <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E71" s="1">
         <v>44000</v>
@@ -2981,16 +2946,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>442</v>
-      </c>
-      <c r="B72" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E72" s="1">
         <v>85000</v>
@@ -2998,16 +2963,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>442</v>
-      </c>
-      <c r="B73" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B73">
+        <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -3015,16 +2980,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>442</v>
-      </c>
-      <c r="B74" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B74">
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -3032,16 +2997,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>442</v>
-      </c>
-      <c r="B75" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B75">
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D75" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -3049,216 +3014,216 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>443</v>
-      </c>
-      <c r="B76" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D76" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E76" s="1">
         <v>185000</v>
       </c>
       <c r="F76" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>443</v>
-      </c>
-      <c r="B77" t="s">
-        <v>6</v>
+        <v>427</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D77" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E77" s="1">
         <v>359000</v>
       </c>
       <c r="F77" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>443</v>
-      </c>
-      <c r="B78" t="s">
-        <v>6</v>
+        <v>427</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D78" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E78" s="1">
         <v>189000</v>
       </c>
       <c r="F78" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>443</v>
-      </c>
-      <c r="B79" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D79" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E79" s="1">
         <v>349000</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>443</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E80" s="1">
         <v>229000</v>
       </c>
       <c r="F80" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>443</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1">
         <v>119000</v>
       </c>
       <c r="F81" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>443</v>
-      </c>
-      <c r="B82" t="s">
-        <v>179</v>
+        <v>427</v>
+      </c>
+      <c r="B82">
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D82" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1">
         <v>299000</v>
       </c>
       <c r="F82" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>443</v>
-      </c>
-      <c r="B83" t="s">
-        <v>179</v>
+        <v>427</v>
+      </c>
+      <c r="B83">
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E83" s="1">
         <v>269000</v>
       </c>
       <c r="F83" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>443</v>
-      </c>
-      <c r="B84" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E84" s="1">
         <v>229000</v>
       </c>
       <c r="F84" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>443</v>
-      </c>
-      <c r="B85" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E85" s="1">
         <v>203000</v>
       </c>
       <c r="F85" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>442</v>
-      </c>
-      <c r="B86" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1">
         <v>30000</v>
@@ -3266,16 +3231,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>442</v>
-      </c>
-      <c r="B87" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B87">
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D87" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E87" s="1">
         <v>40000</v>
@@ -3283,16 +3248,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>442</v>
-      </c>
-      <c r="B88" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D88" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E88" s="1">
         <v>25000</v>
@@ -3300,16 +3265,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>442</v>
-      </c>
-      <c r="B89" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B89">
+        <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E89" s="1">
         <v>25000</v>
@@ -3317,16 +3282,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>442</v>
-      </c>
-      <c r="B90" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D90" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1">
         <v>59000</v>
@@ -3334,16 +3299,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>442</v>
-      </c>
-      <c r="B91" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B91">
+        <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D91" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E91" s="1">
         <v>59000</v>
@@ -3351,16 +3316,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>442</v>
-      </c>
-      <c r="B92" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1">
         <v>59000</v>
@@ -3368,16 +3333,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>442</v>
-      </c>
-      <c r="B93" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E93" s="1">
         <v>59000</v>
@@ -3385,16 +3350,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>442</v>
-      </c>
-      <c r="B94" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B94">
+        <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D94" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E94" s="1">
         <v>64000</v>
@@ -3402,16 +3367,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>442</v>
-      </c>
-      <c r="B95" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B95">
+        <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D95" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E95" s="1">
         <v>59000</v>
@@ -3419,96 +3384,96 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>443</v>
-      </c>
-      <c r="B96" t="s">
-        <v>33</v>
+        <v>427</v>
+      </c>
+      <c r="B96">
+        <v>6</v>
       </c>
       <c r="C96" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D96" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E96" s="1">
         <v>350000</v>
       </c>
       <c r="F96" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>443</v>
-      </c>
-      <c r="B97" t="s">
-        <v>33</v>
+        <v>427</v>
+      </c>
+      <c r="B97">
+        <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D97" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1">
         <v>350000</v>
       </c>
       <c r="F97" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>443</v>
-      </c>
-      <c r="B98" t="s">
-        <v>33</v>
+        <v>427</v>
+      </c>
+      <c r="B98">
+        <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D98" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E98" s="1">
         <v>350000</v>
       </c>
       <c r="F98" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>443</v>
-      </c>
-      <c r="B99" t="s">
-        <v>33</v>
+        <v>427</v>
+      </c>
+      <c r="B99">
+        <v>6</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E99" s="1">
         <v>350000</v>
       </c>
       <c r="F99" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>442</v>
-      </c>
-      <c r="B100" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D100" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E100" s="1">
         <v>60000</v>
@@ -3516,16 +3481,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>442</v>
-      </c>
-      <c r="B101" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B101">
+        <v>6</v>
       </c>
       <c r="C101" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D101" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E101" s="1">
         <v>60000</v>
@@ -3533,16 +3498,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>442</v>
-      </c>
-      <c r="B102" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B102">
+        <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D102" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1">
         <v>60000</v>
@@ -3550,16 +3515,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>442</v>
-      </c>
-      <c r="B103" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B103">
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D103" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1">
         <v>60000</v>
@@ -3567,16 +3532,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>442</v>
-      </c>
-      <c r="B104" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B104">
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D104" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1">
         <v>60000</v>
@@ -3584,16 +3549,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>442</v>
-      </c>
-      <c r="B105" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B105">
+        <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D105" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1">
         <v>60000</v>
@@ -3601,16 +3566,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>442</v>
-      </c>
-      <c r="B106" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B106">
+        <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D106" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E106" s="1">
         <v>60000</v>
@@ -3618,16 +3583,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>442</v>
-      </c>
-      <c r="B107" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B107">
+        <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D107" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E107" s="1">
         <v>60000</v>
@@ -3635,16 +3600,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>442</v>
-      </c>
-      <c r="B108" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B108">
+        <v>6</v>
       </c>
       <c r="C108" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D108" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1">
         <v>60000</v>
@@ -3652,16 +3617,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>442</v>
-      </c>
-      <c r="B109" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B109">
+        <v>6</v>
       </c>
       <c r="C109" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D109" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E109" s="1">
         <v>60000</v>
@@ -3669,16 +3634,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>442</v>
-      </c>
-      <c r="B110" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B110">
+        <v>6</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D110" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E110" s="1">
         <v>60000</v>
@@ -3686,16 +3651,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>442</v>
-      </c>
-      <c r="B111" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B111">
+        <v>6</v>
       </c>
       <c r="C111" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D111" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1">
         <v>60000</v>
@@ -3703,16 +3668,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>442</v>
-      </c>
-      <c r="B112" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B112">
+        <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E112" s="1">
         <v>60000</v>
@@ -3720,16 +3685,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>442</v>
-      </c>
-      <c r="B113" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B113">
+        <v>6</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D113" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E113" s="1">
         <v>60000</v>
@@ -3737,16 +3702,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>442</v>
-      </c>
-      <c r="B114" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B114">
+        <v>6</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D114" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E114" s="1">
         <v>60000</v>
@@ -3754,16 +3719,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>442</v>
-      </c>
-      <c r="B115" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B115">
+        <v>6</v>
       </c>
       <c r="C115" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D115" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E115" s="1">
         <v>60000</v>
@@ -3771,16 +3736,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>442</v>
-      </c>
-      <c r="B116" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B116">
+        <v>6</v>
       </c>
       <c r="C116" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D116" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E116" s="1">
         <v>60000</v>
@@ -3788,16 +3753,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>442</v>
-      </c>
-      <c r="B117" t="s">
-        <v>33</v>
+        <v>426</v>
+      </c>
+      <c r="B117">
+        <v>6</v>
       </c>
       <c r="C117" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E117" s="1">
         <v>60000</v>
@@ -3805,16 +3770,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>442</v>
-      </c>
-      <c r="B118" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D118" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E118" s="1">
         <v>58000</v>
@@ -3822,16 +3787,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>442</v>
-      </c>
-      <c r="B119" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B119">
+        <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D119" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E119" s="1">
         <v>64000</v>
@@ -3839,16 +3804,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>442</v>
-      </c>
-      <c r="B120" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D120" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E120" s="1">
         <v>64000</v>
@@ -3856,16 +3821,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>442</v>
-      </c>
-      <c r="B121" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B121">
+        <v>3</v>
       </c>
       <c r="C121" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1">
         <v>62000</v>
@@ -3873,16 +3838,16 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>442</v>
-      </c>
-      <c r="B122" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B122">
+        <v>10</v>
       </c>
       <c r="C122" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D122" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E122" s="1">
         <v>85000</v>
@@ -3890,16 +3855,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>442</v>
-      </c>
-      <c r="B123" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B123">
+        <v>10</v>
       </c>
       <c r="C123" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D123" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1">
         <v>85000</v>
@@ -3907,16 +3872,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>442</v>
-      </c>
-      <c r="B124" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1">
         <v>25000</v>
@@ -3924,16 +3889,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>442</v>
-      </c>
-      <c r="B125" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B125">
+        <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1">
         <v>85000</v>
@@ -3941,16 +3906,16 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>442</v>
-      </c>
-      <c r="B126" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B126">
+        <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E126" s="1">
         <v>85000</v>
@@ -3958,16 +3923,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>442</v>
-      </c>
-      <c r="B127" t="s">
-        <v>151</v>
+        <v>426</v>
+      </c>
+      <c r="B127">
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E127" s="1">
         <v>85000</v>
@@ -3975,16 +3940,16 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>442</v>
-      </c>
-      <c r="B128" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B128">
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D128" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E128" s="1">
         <v>40000</v>
@@ -3992,16 +3957,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>442</v>
-      </c>
-      <c r="B129" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
       </c>
       <c r="C129" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E129" s="1">
         <v>39000</v>
@@ -4009,96 +3974,96 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>443</v>
-      </c>
-      <c r="B130" t="s">
-        <v>284</v>
+        <v>427</v>
+      </c>
+      <c r="B130">
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="D130" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="E130" s="1">
         <v>429000</v>
       </c>
       <c r="F130" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>443</v>
-      </c>
-      <c r="B131" t="s">
-        <v>284</v>
+        <v>427</v>
+      </c>
+      <c r="B131">
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D131" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E131" s="1">
         <v>629000</v>
       </c>
       <c r="F131" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>443</v>
-      </c>
-      <c r="B132" t="s">
-        <v>284</v>
+        <v>427</v>
+      </c>
+      <c r="B132">
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D132" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="E132" s="1">
         <v>459000</v>
       </c>
       <c r="F132" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>443</v>
-      </c>
-      <c r="B133" t="s">
-        <v>6</v>
+        <v>427</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D133" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1">
         <v>65000</v>
       </c>
       <c r="F133" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>442</v>
-      </c>
-      <c r="B134" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="D134" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1">
         <v>13000</v>
@@ -4106,16 +4071,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>442</v>
-      </c>
-      <c r="B135" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B135">
+        <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D135" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E135" s="1">
         <v>30000</v>
@@ -4123,16 +4088,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>442</v>
-      </c>
-      <c r="B136" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D136" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1">
         <v>50000</v>
@@ -4140,16 +4105,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>442</v>
-      </c>
-      <c r="B137" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
       </c>
       <c r="C137" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D137" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="E137" s="1">
         <v>25000</v>
@@ -4157,16 +4122,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>442</v>
-      </c>
-      <c r="B138" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B138">
+        <v>11</v>
       </c>
       <c r="C138" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D138" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="E138" s="1">
         <v>5000</v>
@@ -4174,16 +4139,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>442</v>
-      </c>
-      <c r="B139" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B139">
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D139" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="E139" s="1">
         <v>30000</v>
@@ -4191,16 +4156,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>442</v>
-      </c>
-      <c r="B140" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B140">
+        <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D140" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="E140" s="1">
         <v>30000</v>
@@ -4208,16 +4173,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>442</v>
-      </c>
-      <c r="B141" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B141">
+        <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="D141" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E141" s="1">
         <v>30000</v>
@@ -4225,16 +4190,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>442</v>
-      </c>
-      <c r="B142" t="s">
-        <v>154</v>
+        <v>426</v>
+      </c>
+      <c r="B142">
+        <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D142" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1">
         <v>119000</v>
@@ -4242,16 +4207,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>442</v>
-      </c>
-      <c r="B143" t="s">
-        <v>315</v>
+        <v>426</v>
+      </c>
+      <c r="B143">
+        <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="D143" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1">
         <v>49000</v>
@@ -4259,36 +4224,36 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>443</v>
-      </c>
-      <c r="B144" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B144">
+        <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="D144" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1">
         <v>160000</v>
       </c>
       <c r="F144" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>442</v>
-      </c>
-      <c r="B145" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B145">
+        <v>15</v>
       </c>
       <c r="C145" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D145" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="E145" s="1">
         <v>50000</v>
@@ -4296,16 +4261,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>442</v>
-      </c>
-      <c r="B146" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B146">
+        <v>15</v>
       </c>
       <c r="C146" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="D146" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="E146" s="1">
         <v>50000</v>
@@ -4313,16 +4278,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>442</v>
-      </c>
-      <c r="B147" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B147">
+        <v>15</v>
       </c>
       <c r="C147" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="D147" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="E147" s="1">
         <v>50000</v>
@@ -4330,16 +4295,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>442</v>
-      </c>
-      <c r="B148" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B148">
+        <v>15</v>
       </c>
       <c r="C148" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D148" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1">
         <v>50000</v>
@@ -4347,16 +4312,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>442</v>
-      </c>
-      <c r="B149" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B149">
+        <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="D149" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="E149" s="1">
         <v>50000</v>
@@ -4364,16 +4329,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>442</v>
-      </c>
-      <c r="B150" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B150">
+        <v>15</v>
       </c>
       <c r="C150" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D150" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="E150" s="1">
         <v>50000</v>
@@ -4381,16 +4346,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>442</v>
-      </c>
-      <c r="B151" t="s">
-        <v>321</v>
+        <v>426</v>
+      </c>
+      <c r="B151">
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D151" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1">
         <v>50000</v>
@@ -4398,16 +4363,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>442</v>
-      </c>
-      <c r="B152" t="s">
+        <v>426</v>
+      </c>
+      <c r="B152">
+        <v>15</v>
+      </c>
+      <c r="C152" t="s">
         <v>321</v>
       </c>
-      <c r="C152" t="s">
-        <v>336</v>
-      </c>
       <c r="D152" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E152" s="1">
         <v>50000</v>
@@ -4415,36 +4380,36 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>443</v>
-      </c>
-      <c r="B153" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
       </c>
       <c r="C153" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D153" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1">
         <v>160000</v>
       </c>
       <c r="F153" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>442</v>
-      </c>
-      <c r="B154" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
       </c>
       <c r="C154" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D154" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="E154" s="1">
         <v>40000</v>
@@ -4452,16 +4417,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>442</v>
-      </c>
-      <c r="B155" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D155" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
@@ -4469,16 +4434,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>442</v>
-      </c>
-      <c r="B156" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D156" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1">
         <v>0</v>
@@ -4486,36 +4451,36 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>443</v>
-      </c>
-      <c r="B157" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B157">
+        <v>3</v>
       </c>
       <c r="C157" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="D157" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="E157" s="1">
         <v>250000</v>
       </c>
       <c r="F157" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>442</v>
-      </c>
-      <c r="B158" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
       </c>
       <c r="C158" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="D158" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1">
         <v>59000</v>
@@ -4523,16 +4488,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>442</v>
-      </c>
-      <c r="B159" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B159">
+        <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="D159" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="E159" s="1">
         <v>5000</v>
@@ -4540,16 +4505,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>442</v>
-      </c>
-      <c r="B160" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B160">
+        <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="D160" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E160" s="1">
         <v>5000</v>
@@ -4557,36 +4522,36 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>443</v>
-      </c>
-      <c r="B161" t="s">
-        <v>19</v>
+        <v>427</v>
+      </c>
+      <c r="B161">
+        <v>3</v>
       </c>
       <c r="C161" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D161" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="E161" s="1">
         <v>250000</v>
       </c>
       <c r="F161" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>442</v>
-      </c>
-      <c r="B162" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B162">
+        <v>3</v>
       </c>
       <c r="C162" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D162" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1">
         <v>59000</v>
@@ -4594,16 +4559,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>442</v>
-      </c>
-      <c r="B163" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B163">
+        <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D163" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E163" s="1">
         <v>59000</v>
@@ -4611,16 +4576,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>442</v>
-      </c>
-      <c r="B164" t="s">
-        <v>362</v>
+        <v>426</v>
+      </c>
+      <c r="B164">
+        <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="D164" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="E164" s="1">
         <v>36000</v>
@@ -4628,16 +4593,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>442</v>
-      </c>
-      <c r="B165" t="s">
-        <v>362</v>
+        <v>426</v>
+      </c>
+      <c r="B165">
+        <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="D165" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1">
         <v>44000</v>
@@ -4645,16 +4610,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>442</v>
-      </c>
-      <c r="B166" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B166">
+        <v>3</v>
       </c>
       <c r="C166" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="D166" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="E166" s="1">
         <v>59000</v>
@@ -4662,16 +4627,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>442</v>
-      </c>
-      <c r="B167" t="s">
-        <v>362</v>
+        <v>426</v>
+      </c>
+      <c r="B167">
+        <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D167" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1">
         <v>36000</v>
@@ -4679,16 +4644,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>442</v>
-      </c>
-      <c r="B168" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B168">
+        <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D168" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1">
         <v>58000</v>
@@ -4696,16 +4661,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>442</v>
-      </c>
-      <c r="B169" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B169">
+        <v>3</v>
       </c>
       <c r="C169" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D169" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="E169" s="1">
         <v>58000</v>
@@ -4713,36 +4678,36 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>443</v>
-      </c>
-      <c r="B170" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
       </c>
       <c r="C170" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="D170" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="E170" s="1">
         <v>175000</v>
       </c>
       <c r="F170" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>442</v>
-      </c>
-      <c r="B171" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B171">
+        <v>5</v>
       </c>
       <c r="C171" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="D171" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1">
         <v>5000</v>
@@ -4750,36 +4715,36 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>443</v>
-      </c>
-      <c r="B172" t="s">
-        <v>179</v>
+        <v>427</v>
+      </c>
+      <c r="B172">
+        <v>12</v>
       </c>
       <c r="C172" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="D172" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="E172" s="1">
         <v>230000</v>
       </c>
       <c r="F172" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>442</v>
-      </c>
-      <c r="B173" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
       </c>
       <c r="C173" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D173" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E173" s="1">
         <v>30000</v>
@@ -4787,16 +4752,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>442</v>
-      </c>
-      <c r="B174" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B174">
+        <v>12</v>
       </c>
       <c r="C174" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="D174" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="E174" s="1">
         <v>40000</v>
@@ -4804,16 +4769,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>442</v>
-      </c>
-      <c r="B175" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
       </c>
       <c r="C175" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="D175" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="E175" s="1">
         <v>0</v>
@@ -4821,16 +4786,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>442</v>
-      </c>
-      <c r="B176" t="s">
-        <v>28</v>
+        <v>426</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="D176" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="E176" s="1">
         <v>50000</v>
@@ -4838,16 +4803,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>442</v>
-      </c>
-      <c r="B177" t="s">
-        <v>6</v>
+        <v>426</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
       </c>
       <c r="C177" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="D177" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="E177" s="1">
         <v>53000</v>
@@ -4855,16 +4820,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>442</v>
-      </c>
-      <c r="B178" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B178">
+        <v>3</v>
       </c>
       <c r="C178" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D178" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="E178" s="1">
         <v>69000</v>
@@ -4872,56 +4837,56 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>443</v>
-      </c>
-      <c r="B179" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B179">
+        <v>4</v>
       </c>
       <c r="C179" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="D179" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E179" s="1">
         <v>133000</v>
       </c>
       <c r="F179" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>443</v>
-      </c>
-      <c r="B180" t="s">
-        <v>179</v>
+        <v>427</v>
+      </c>
+      <c r="B180">
+        <v>12</v>
       </c>
       <c r="C180" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="D180" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="E180" s="1">
         <v>174000</v>
       </c>
       <c r="F180" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>442</v>
-      </c>
-      <c r="B181" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
       </c>
       <c r="C181" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="D181" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="E181" s="1">
         <v>30000</v>
@@ -4929,16 +4894,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>442</v>
-      </c>
-      <c r="B182" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B182">
+        <v>12</v>
       </c>
       <c r="C182" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="D182" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="E182" s="1">
         <v>40000</v>
@@ -4946,36 +4911,36 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>443</v>
-      </c>
-      <c r="B183" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
       </c>
       <c r="C183" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D183" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1">
         <v>105000</v>
       </c>
       <c r="F183" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>442</v>
-      </c>
-      <c r="B184" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B184">
+        <v>4</v>
       </c>
       <c r="C184" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="D184" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="E184" s="1">
         <v>30000</v>
@@ -4983,16 +4948,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>442</v>
-      </c>
-      <c r="B185" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B185">
+        <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="D185" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1">
         <v>30000</v>
@@ -5000,16 +4965,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>442</v>
-      </c>
-      <c r="B186" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B186">
+        <v>4</v>
       </c>
       <c r="C186" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="D186" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1">
         <v>30000</v>
@@ -5017,16 +4982,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>442</v>
-      </c>
-      <c r="B187" t="s">
-        <v>25</v>
+        <v>426</v>
+      </c>
+      <c r="B187">
+        <v>4</v>
       </c>
       <c r="C187" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="D187" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="E187" s="1">
         <v>30000</v>
@@ -5034,16 +4999,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>442</v>
-      </c>
-      <c r="B188" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B188">
+        <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D188" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="E188" s="1">
         <v>68000</v>
@@ -5051,16 +5016,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>442</v>
-      </c>
-      <c r="B189" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
       </c>
       <c r="C189" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="D189" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="E189" s="1">
         <v>68000</v>
@@ -5068,16 +5033,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>442</v>
-      </c>
-      <c r="B190" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B190">
+        <v>3</v>
       </c>
       <c r="C190" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="D190" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="E190" s="1">
         <v>68000</v>
@@ -5085,16 +5050,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>442</v>
-      </c>
-      <c r="B191" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B191">
+        <v>3</v>
       </c>
       <c r="C191" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="D191" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1">
         <v>63000</v>
@@ -5102,16 +5067,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>442</v>
-      </c>
-      <c r="B192" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="D192" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E192" s="1">
         <v>59000</v>
@@ -5119,16 +5084,16 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>442</v>
-      </c>
-      <c r="B193" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
       </c>
       <c r="C193" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="D193" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="E193" s="1">
         <v>59000</v>
@@ -5136,16 +5101,16 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>442</v>
-      </c>
-      <c r="B194" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B194">
+        <v>3</v>
       </c>
       <c r="C194" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="D194" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="E194" s="1">
         <v>63000</v>
@@ -5153,16 +5118,16 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>442</v>
-      </c>
-      <c r="B195" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B195">
+        <v>3</v>
       </c>
       <c r="C195" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E195" s="1">
         <v>58000</v>
@@ -5170,16 +5135,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>442</v>
-      </c>
-      <c r="B196" t="s">
-        <v>19</v>
+        <v>426</v>
+      </c>
+      <c r="B196">
+        <v>3</v>
       </c>
       <c r="C196" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="E196" s="1">
         <v>58000</v>
@@ -5187,16 +5152,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>442</v>
-      </c>
-      <c r="B197" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B197">
+        <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="E197" s="1">
         <v>40000</v>
@@ -5204,16 +5169,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>442</v>
-      </c>
-      <c r="B198" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B198">
+        <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E198" s="1">
         <v>40000</v>
@@ -5221,16 +5186,16 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>442</v>
-      </c>
-      <c r="B199" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B199">
+        <v>12</v>
       </c>
       <c r="C199" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="E199" s="1">
         <v>40000</v>
@@ -5238,16 +5203,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>442</v>
-      </c>
-      <c r="B200" t="s">
-        <v>179</v>
+        <v>426</v>
+      </c>
+      <c r="B200">
+        <v>12</v>
       </c>
       <c r="C200" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="E200" s="1">
         <v>40000</v>
